--- a/data/trans_dic/PCS12_SP_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R3-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12)</t>
+          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,67; 20,33</t>
+          <t>14,42; 20,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,25; 22,09</t>
+          <t>16,25; 22,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,38; 22,37</t>
+          <t>16,23; 22,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,76; 30,45</t>
+          <t>23,58; 30,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,88; 30,44</t>
+          <t>24,13; 30,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,74; 34,92</t>
+          <t>27,73; 34,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,54; 33,8</t>
+          <t>26,58; 33,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,81; 35,16</t>
+          <t>29,66; 35,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,96; 24,43</t>
+          <t>20,21; 24,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,86; 27,66</t>
+          <t>22,83; 27,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22,31; 27,06</t>
+          <t>22,48; 27,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,58; 32,3</t>
+          <t>27,45; 31,95</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,94; 16,59</t>
+          <t>12,13; 16,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,29; 21,39</t>
+          <t>16,18; 21,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,19; 18,74</t>
+          <t>14,19; 18,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,56; 65,29</t>
+          <t>17,56; 64,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,58; 30,43</t>
+          <t>24,63; 30,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,07; 32,52</t>
+          <t>26,88; 32,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,61; 29,27</t>
+          <t>23,75; 29,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,74; 32,39</t>
+          <t>27,6; 32,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,05; 22,81</t>
+          <t>19,06; 22,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,27; 26,29</t>
+          <t>22,33; 26,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,58; 23,3</t>
+          <t>19,6; 23,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,78; 53,46</t>
+          <t>23,66; 55,77</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,48; 20,21</t>
+          <t>14,5; 20,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,59; 17,08</t>
+          <t>11,77; 17,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,12; 17,42</t>
+          <t>12,33; 17,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,66; 24,15</t>
+          <t>18,08; 24,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,68; 32,29</t>
+          <t>25,71; 32,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,77; 29,62</t>
+          <t>22,99; 29,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,09; 26,35</t>
+          <t>20,22; 26,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,08; 27,26</t>
+          <t>10,95; 26,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,77; 25,29</t>
+          <t>20,71; 25,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,99; 22,27</t>
+          <t>17,96; 22,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,93; 21,26</t>
+          <t>17,02; 21,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,51; 24,08</t>
+          <t>13,21; 24,0</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,25; 17,61</t>
+          <t>13,3; 17,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,7; 21,92</t>
+          <t>16,59; 22,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,64; 19,62</t>
+          <t>14,37; 19,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,26; 24,33</t>
+          <t>18,92; 24,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,48; 28,78</t>
+          <t>23,43; 29,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,67; 32,36</t>
+          <t>26,77; 32,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,6; 28,26</t>
+          <t>22,58; 28,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,6; 33,79</t>
+          <t>24,86; 33,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,13; 22,64</t>
+          <t>19,22; 22,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,77; 26,72</t>
+          <t>22,46; 26,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19,61; 23,38</t>
+          <t>19,68; 23,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,27; 28,65</t>
+          <t>23,19; 28,55</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,65; 17,11</t>
+          <t>14,48; 17,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,72; 19,22</t>
+          <t>16,61; 19,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,43; 17,96</t>
+          <t>15,5; 18,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,12; 46,85</t>
+          <t>21,09; 42,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,62; 28,75</t>
+          <t>25,71; 28,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,55; 30,6</t>
+          <t>27,49; 30,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,67; 27,76</t>
+          <t>24,69; 27,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,57; 30,69</t>
+          <t>22,89; 30,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,52; 22,62</t>
+          <t>20,48; 22,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,61; 24,69</t>
+          <t>22,64; 24,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20,46; 22,54</t>
+          <t>20,49; 22,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,18; 35,49</t>
+          <t>24,29; 36,84</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12)</t>
+          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>101780; 141063</t>
+          <t>100063; 139827</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>114343; 155413</t>
+          <t>114301; 157389</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>110565; 150924</t>
+          <t>109550; 150010</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>149746; 191898</t>
+          <t>148563; 191841</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>164376; 209516</t>
+          <t>166084; 212524</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>193353; 243429</t>
+          <t>193264; 241667</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>178563; 227397</t>
+          <t>178870; 227295</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>199655; 235497</t>
+          <t>198649; 236863</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>275894; 337643</t>
+          <t>279384; 338723</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>320198; 387329</t>
+          <t>319734; 383544</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>300691; 364661</t>
+          <t>302991; 364135</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>358551; 419912</t>
+          <t>356906; 415306</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>114846; 159545</t>
+          <t>116707; 159792</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>165793; 217689</t>
+          <t>164691; 215250</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>145064; 191568</t>
+          <t>145044; 190585</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>208637; 775867</t>
+          <t>208615; 771009</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>238067; 294711</t>
+          <t>238487; 296849</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>279426; 335656</t>
+          <t>277496; 338333</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>246281; 305267</t>
+          <t>247714; 305952</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>264318; 308668</t>
+          <t>262950; 309740</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>367627; 440241</t>
+          <t>367820; 440146</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>456625; 538944</t>
+          <t>457801; 536202</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>404420; 481274</t>
+          <t>404782; 483879</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>509243; 1144651</t>
+          <t>506662; 1194189</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>98281; 137105</t>
+          <t>98367; 138471</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>87776; 129428</t>
+          <t>89207; 130850</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92026; 132331</t>
+          <t>93656; 133094</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>124055; 169626</t>
+          <t>126983; 169025</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>175589; 220819</t>
+          <t>175794; 219890</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>176979; 230203</t>
+          <t>178673; 229538</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>157742; 206836</t>
+          <t>158724; 208958</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>103212; 253933</t>
+          <t>101982; 251423</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>282969; 344565</t>
+          <t>282166; 342663</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>276143; 341874</t>
+          <t>275715; 342770</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>261439; 328349</t>
+          <t>262957; 327242</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>220789; 393452</t>
+          <t>215880; 392223</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>124841; 165887</t>
+          <t>125288; 166175</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>158297; 207779</t>
+          <t>157260; 209473</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>137276; 183979</t>
+          <t>134770; 182187</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>177770; 224588</t>
+          <t>174624; 224364</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>243847; 298938</t>
+          <t>243391; 302150</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>280495; 340443</t>
+          <t>281547; 344000</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>235940; 294993</t>
+          <t>235677; 295766</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>268013; 368065</t>
+          <t>270758; 370080</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>378861; 448421</t>
+          <t>380790; 451270</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>455306; 534213</t>
+          <t>449055; 530738</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>388456; 463191</t>
+          <t>389981; 464743</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>468274; 576518</t>
+          <t>466604; 574401</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>479996; 560644</t>
+          <t>474454; 560810</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>573040; 658524</t>
+          <t>569321; 661015</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>523746; 609668</t>
+          <t>525968; 616499</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>727315; 1613373</t>
+          <t>726198; 1480569</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>865860; 971428</t>
+          <t>868738; 973390</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>980169; 1088966</t>
+          <t>978146; 1093802</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>874369; 984036</t>
+          <t>875309; 985535</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>858752; 1118072</t>
+          <t>833870; 1116157</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1365870; 1505658</t>
+          <t>1362956; 1504916</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1579453; 1724670</t>
+          <t>1581308; 1725508</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1419595; 1563796</t>
+          <t>1422095; 1562434</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1713593; 2514992</t>
+          <t>1721211; 2611019</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/PCS12_SP_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R3-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,42; 20,15</t>
+          <t>14,45; 20,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,25; 22,37</t>
+          <t>16,42; 22,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,23; 22,23</t>
+          <t>16,14; 22,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,58; 30,44</t>
+          <t>23,61; 30,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,13; 30,87</t>
+          <t>24,09; 30,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,73; 34,67</t>
+          <t>27,37; 34,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,58; 33,78</t>
+          <t>26,24; 33,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,66; 35,36</t>
+          <t>29,11; 34,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,21; 24,5</t>
+          <t>19,83; 24,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,83; 27,39</t>
+          <t>22,77; 27,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22,48; 27,02</t>
+          <t>22,43; 27,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,45; 31,95</t>
+          <t>26,9; 31,42</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,13; 16,61</t>
+          <t>11,81; 16,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,18; 21,15</t>
+          <t>16,07; 21,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,19; 18,64</t>
+          <t>14,0; 18,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,56; 64,88</t>
+          <t>16,04; 20,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,63; 30,65</t>
+          <t>24,35; 30,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,88; 32,78</t>
+          <t>26,82; 32,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,75; 29,34</t>
+          <t>23,5; 28,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,6; 32,51</t>
+          <t>27,72; 32,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,06; 22,8</t>
+          <t>19,07; 22,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,33; 26,15</t>
+          <t>22,02; 26,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,6; 23,43</t>
+          <t>19,81; 23,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,66; 55,77</t>
+          <t>22,36; 25,8</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,5; 20,41</t>
+          <t>14,4; 20,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,77; 17,27</t>
+          <t>11,7; 17,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,33; 17,52</t>
+          <t>12,37; 17,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,08; 24,07</t>
+          <t>17,41; 23,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,71; 32,16</t>
+          <t>25,22; 32,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,99; 29,53</t>
+          <t>22,92; 29,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,22; 26,62</t>
+          <t>20,29; 26,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,95; 26,99</t>
+          <t>24,07; 29,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,71; 25,15</t>
+          <t>20,66; 25,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,96; 22,33</t>
+          <t>18,0; 22,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,02; 21,19</t>
+          <t>17,0; 21,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,21; 24,0</t>
+          <t>21,38; 25,66</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,3; 17,64</t>
+          <t>13,02; 17,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,59; 22,1</t>
+          <t>16,71; 22,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,37; 19,43</t>
+          <t>14,38; 19,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,92; 24,31</t>
+          <t>18,5; 23,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,43; 29,09</t>
+          <t>23,4; 28,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,77; 32,7</t>
+          <t>26,71; 32,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,58; 28,34</t>
+          <t>22,59; 28,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,86; 33,97</t>
+          <t>30,16; 35,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,22; 22,78</t>
+          <t>19,15; 22,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,46; 26,54</t>
+          <t>22,56; 26,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19,68; 23,46</t>
+          <t>19,5; 23,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,19; 28,55</t>
+          <t>25,47; 28,82</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,48; 17,12</t>
+          <t>14,68; 17,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,61; 19,29</t>
+          <t>16,44; 19,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,5; 18,16</t>
+          <t>15,46; 18,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,09; 42,99</t>
+          <t>19,83; 22,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,71; 28,81</t>
+          <t>25,72; 28,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,49; 30,74</t>
+          <t>27,51; 30,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,69; 27,8</t>
+          <t>24,49; 27,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,89; 30,63</t>
+          <t>29,1; 31,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,48; 22,61</t>
+          <t>20,61; 22,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,64; 24,7</t>
+          <t>22,65; 24,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20,49; 22,52</t>
+          <t>20,43; 22,54</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,29; 36,84</t>
+          <t>24,92; 26,82</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>170073</t>
+          <t>183022</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>216797</t>
+          <t>230440</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>386870</t>
+          <t>413462</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>100063; 139827</t>
+          <t>100251; 138986</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>114301; 157389</t>
+          <t>115499; 156193</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109550; 150010</t>
+          <t>108901; 149257</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148563; 191841</t>
+          <t>161694; 207645</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>166084; 212524</t>
+          <t>165809; 211129</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>193264; 241667</t>
+          <t>190788; 240873</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>178870; 227295</t>
+          <t>176547; 227569</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>198649; 236863</t>
+          <t>211635; 250992</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>279384; 338723</t>
+          <t>274102; 336706</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>319734; 383544</t>
+          <t>318853; 385238</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>302991; 364135</t>
+          <t>302315; 367656</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>356906; 415306</t>
+          <t>379792; 443524</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417508</t>
+          <t>190371</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>286008</t>
+          <t>318793</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>703517</t>
+          <t>509164</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>116707; 159792</t>
+          <t>113582; 157809</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>164691; 215250</t>
+          <t>163614; 214358</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>145044; 190585</t>
+          <t>143128; 194074</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>208615; 771009</t>
+          <t>167483; 218824</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>238487; 296849</t>
+          <t>235792; 291770</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>277496; 338333</t>
+          <t>276863; 339456</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>247714; 305952</t>
+          <t>245037; 302099</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>262950; 309740</t>
+          <t>295272; 348020</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>367820; 440146</t>
+          <t>368070; 441499</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>457801; 536202</t>
+          <t>451524; 534393</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>404782; 483879</t>
+          <t>409163; 484121</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>506662; 1194189</t>
+          <t>471634; 544161</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>145981</t>
+          <t>162309</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>188471</t>
+          <t>215696</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>334452</t>
+          <t>378005</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>98367; 138471</t>
+          <t>97707; 136916</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>89207; 130850</t>
+          <t>88659; 130778</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93656; 133094</t>
+          <t>93928; 135195</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126983; 169025</t>
+          <t>139321; 187580</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>175794; 219890</t>
+          <t>172460; 220333</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>178673; 229538</t>
+          <t>178162; 228240</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>158724; 208958</t>
+          <t>159248; 208170</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>101982; 251423</t>
+          <t>195083; 237931</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>282166; 342663</t>
+          <t>281438; 344494</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>275715; 342770</t>
+          <t>276317; 342856</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>262957; 327242</t>
+          <t>262565; 326673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>215880; 392223</t>
+          <t>344448; 413251</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>199103</t>
+          <t>208074</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>334039</t>
+          <t>362134</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>533142</t>
+          <t>570208</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>125288; 166175</t>
+          <t>122703; 165835</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>157260; 209473</t>
+          <t>158357; 210117</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>134770; 182187</t>
+          <t>134846; 182004</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>174624; 224364</t>
+          <t>182396; 233664</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>243391; 302150</t>
+          <t>242994; 299325</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>281547; 344000</t>
+          <t>280915; 343365</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>235677; 295766</t>
+          <t>235837; 295249</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>270758; 370080</t>
+          <t>335674; 390485</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>380790; 451270</t>
+          <t>379296; 451987</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>449055; 530738</t>
+          <t>451125; 532131</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>389981; 464743</t>
+          <t>386377; 465080</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>466604; 574401</t>
+          <t>534627; 604935</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>932665</t>
+          <t>743776</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1025315</t>
+          <t>1127063</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1957981</t>
+          <t>1870839</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>474454; 560810</t>
+          <t>481030; 562924</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>569321; 661015</t>
+          <t>563457; 658834</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>525968; 616499</t>
+          <t>524766; 611561</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>726198; 1480569</t>
+          <t>697179; 789609</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>868738; 973390</t>
+          <t>869194; 978300</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>978146; 1093802</t>
+          <t>978744; 1093225</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>875309; 985535</t>
+          <t>867949; 987318</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>833870; 1116157</t>
+          <t>1081305; 1176427</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1362956; 1504916</t>
+          <t>1371871; 1505426</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1581308; 1725508</t>
+          <t>1581783; 1722356</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1422095; 1562434</t>
+          <t>1417794; 1563877</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1721211; 2611019</t>
+          <t>1801687; 1939504</t>
         </is>
       </c>
     </row>
